--- a/output/Data and Chart Outputs/south_korea_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/south_korea_power_capacity.xlsx
@@ -1642,7 +1642,7 @@
         <v>44958</v>
       </c>
       <c r="B27" t="n">
-        <v>6.501115400000001</v>
+        <v>6.5011154</v>
       </c>
       <c r="C27" t="n">
         <v>41.201457</v>
@@ -1671,7 +1671,7 @@
         <v>44986</v>
       </c>
       <c r="B28" t="n">
-        <v>6.501115400000001</v>
+        <v>6.5011154</v>
       </c>
       <c r="C28" t="n">
         <v>41.201457</v>
@@ -2425,7 +2425,7 @@
         <v>45778</v>
       </c>
       <c r="B54" t="n">
-        <v>6.514276400000001</v>
+        <v>6.5142764</v>
       </c>
       <c r="C54" t="n">
         <v>45.20385599999999</v>
@@ -2454,7 +2454,7 @@
         <v>45809</v>
       </c>
       <c r="B55" t="n">
-        <v>6.514276400000001</v>
+        <v>6.5142764</v>
       </c>
       <c r="C55" t="n">
         <v>45.20385599999999</v>
@@ -3776,7 +3776,7 @@
         <v>2107.081</v>
       </c>
       <c r="U12" t="n">
-        <v>958.2</v>
+        <v>958.1999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -3841,7 +3841,7 @@
         <v>2107.081</v>
       </c>
       <c r="U13" t="n">
-        <v>958.2</v>
+        <v>958.1999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -4027,7 +4027,7 @@
         <v>117996.004074</v>
       </c>
       <c r="R16" t="n">
-        <v>6489.865400000001</v>
+        <v>6489.8654</v>
       </c>
       <c r="S16" t="n">
         <v>36898.737</v>
@@ -4092,7 +4092,7 @@
         <v>117996.004074</v>
       </c>
       <c r="R17" t="n">
-        <v>6489.865400000001</v>
+        <v>6489.8654</v>
       </c>
       <c r="S17" t="n">
         <v>36898.737</v>
@@ -4157,7 +4157,7 @@
         <v>118265.790804</v>
       </c>
       <c r="R18" t="n">
-        <v>6489.865400000001</v>
+        <v>6489.8654</v>
       </c>
       <c r="S18" t="n">
         <v>36898.737</v>
@@ -4222,7 +4222,7 @@
         <v>119091.658668</v>
       </c>
       <c r="R19" t="n">
-        <v>6490.410400000001</v>
+        <v>6490.4104</v>
       </c>
       <c r="S19" t="n">
         <v>36898.737</v>
@@ -4287,7 +4287,7 @@
         <v>119350.36177</v>
       </c>
       <c r="R20" t="n">
-        <v>6493.410400000001</v>
+        <v>6493.4104</v>
       </c>
       <c r="S20" t="n">
         <v>36991.777</v>
@@ -4352,7 +4352,7 @@
         <v>119350.36177</v>
       </c>
       <c r="R21" t="n">
-        <v>6493.410400000001</v>
+        <v>6493.4104</v>
       </c>
       <c r="S21" t="n">
         <v>36991.777</v>
@@ -4417,7 +4417,7 @@
         <v>119825.8939190013</v>
       </c>
       <c r="R22" t="n">
-        <v>6493.410400000001</v>
+        <v>6493.4104</v>
       </c>
       <c r="S22" t="n">
         <v>36991.777</v>
@@ -4482,7 +4482,7 @@
         <v>119825.8939190013</v>
       </c>
       <c r="R23" t="n">
-        <v>6493.410400000001</v>
+        <v>6493.4104</v>
       </c>
       <c r="S23" t="n">
         <v>36991.777</v>
@@ -4547,7 +4547,7 @@
         <v>119825.8939190013</v>
       </c>
       <c r="R24" t="n">
-        <v>6493.410400000001</v>
+        <v>6493.4104</v>
       </c>
       <c r="S24" t="n">
         <v>36991.777</v>
@@ -4872,7 +4872,7 @@
         <v>124023.0058360019</v>
       </c>
       <c r="R29" t="n">
-        <v>6496.133400000001</v>
+        <v>6496.1334</v>
       </c>
       <c r="S29" t="n">
         <v>36991.782</v>
@@ -4937,7 +4937,7 @@
         <v>124392.1788360018</v>
       </c>
       <c r="R30" t="n">
-        <v>6496.133400000001</v>
+        <v>6496.1334</v>
       </c>
       <c r="S30" t="n">
         <v>36991.782</v>
@@ -5011,7 +5011,7 @@
         <v>899.6510000000002</v>
       </c>
       <c r="U31" t="n">
-        <v>2244.367999999999</v>
+        <v>2244.368</v>
       </c>
     </row>
     <row r="32">
@@ -5141,7 +5141,7 @@
         <v>899.5560000000002</v>
       </c>
       <c r="U33" t="n">
-        <v>2289.117999999999</v>
+        <v>2289.118</v>
       </c>
     </row>
     <row r="34">
@@ -5206,7 +5206,7 @@
         <v>899.5560000000002</v>
       </c>
       <c r="U34" t="n">
-        <v>2289.117999999999</v>
+        <v>2289.118</v>
       </c>
     </row>
     <row r="35">
@@ -5271,7 +5271,7 @@
         <v>898.9060000000001</v>
       </c>
       <c r="U35" t="n">
-        <v>2278.759999999999</v>
+        <v>2278.76</v>
       </c>
     </row>
     <row r="36">
@@ -5336,7 +5336,7 @@
         <v>908.311</v>
       </c>
       <c r="U36" t="n">
-        <v>2339.599999999999</v>
+        <v>2339.6</v>
       </c>
     </row>
     <row r="37">
@@ -7472,7 +7472,7 @@
         <v>138846.305280003</v>
       </c>
       <c r="R69" t="n">
-        <v>6501.115400000001</v>
+        <v>6501.1154</v>
       </c>
       <c r="S69" t="n">
         <v>38127.882</v>
@@ -7537,7 +7537,7 @@
         <v>139048.766610003</v>
       </c>
       <c r="R70" t="n">
-        <v>6501.115400000001</v>
+        <v>6501.1154</v>
       </c>
       <c r="S70" t="n">
         <v>38127.882</v>
@@ -7546,7 +7546,7 @@
         <v>1805.095</v>
       </c>
       <c r="U70" t="n">
-        <v>1940.549</v>
+        <v>1940.548999999999</v>
       </c>
     </row>
     <row r="71">
@@ -7936,7 +7936,7 @@
         <v>1811.467</v>
       </c>
       <c r="U76" t="n">
-        <v>2086.663999999999</v>
+        <v>2086.664</v>
       </c>
     </row>
     <row r="77">
@@ -8456,7 +8456,7 @@
         <v>1846.697</v>
       </c>
       <c r="U84" t="n">
-        <v>2080.973999999999</v>
+        <v>2080.974</v>
       </c>
     </row>
     <row r="85">
@@ -8976,7 +8976,7 @@
         <v>1845.647</v>
       </c>
       <c r="U92" t="n">
-        <v>2155.686999999999</v>
+        <v>2155.687</v>
       </c>
     </row>
     <row r="93">
@@ -9227,7 +9227,7 @@
         <v>154672.739018002</v>
       </c>
       <c r="R96" t="n">
-        <v>6514.276400000001</v>
+        <v>6514.2764</v>
       </c>
       <c r="S96" t="n">
         <v>41267.882</v>
@@ -9292,7 +9292,7 @@
         <v>154916.692799002</v>
       </c>
       <c r="R97" t="n">
-        <v>6514.276400000001</v>
+        <v>6514.2764</v>
       </c>
       <c r="S97" t="n">
         <v>41267.882</v>
@@ -9496,7 +9496,7 @@
         <v>1845.6072</v>
       </c>
       <c r="U100" t="n">
-        <v>2289.726999999999</v>
+        <v>2289.727</v>
       </c>
     </row>
     <row r="101">
@@ -9561,7 +9561,7 @@
         <v>1841.0072</v>
       </c>
       <c r="U101" t="n">
-        <v>2295.726999999999</v>
+        <v>2295.727</v>
       </c>
     </row>
     <row r="102">
@@ -9626,7 +9626,7 @@
         <v>1841.4212</v>
       </c>
       <c r="U102" t="n">
-        <v>2298.126999999999</v>
+        <v>2298.127</v>
       </c>
     </row>
     <row r="103">
@@ -10016,7 +10016,7 @@
         <v>1843.4212</v>
       </c>
       <c r="U108" t="n">
-        <v>2523.496999999999</v>
+        <v>2523.497</v>
       </c>
     </row>
     <row r="109">

--- a/output/Data and Chart Outputs/south_korea_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/south_korea_power_capacity.xlsx
@@ -20,8 +20,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -61,12 +61,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -818,7 +819,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -833,7 +833,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
@@ -913,7 +912,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -942,7 +941,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -971,7 +970,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -1000,7 +999,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -1029,7 +1028,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -1058,7 +1057,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -1087,7 +1086,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -1116,7 +1115,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -1145,7 +1144,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -1174,7 +1173,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -1203,7 +1202,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -1232,7 +1231,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -1261,7 +1260,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -1290,7 +1289,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -1319,7 +1318,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -1348,7 +1347,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -1377,7 +1376,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -1406,7 +1405,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -1435,7 +1434,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -1464,7 +1463,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -1493,7 +1492,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -1522,7 +1521,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -1551,7 +1550,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -1580,7 +1579,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -1609,7 +1608,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -1638,7 +1637,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -1667,7 +1666,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -1696,7 +1695,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -1725,7 +1724,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -1754,7 +1753,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -1783,7 +1782,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -1812,7 +1811,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -1841,7 +1840,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -1870,7 +1869,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -1899,7 +1898,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -1928,7 +1927,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -1957,7 +1956,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -1986,7 +1985,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -2015,7 +2014,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -2044,7 +2043,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -2073,7 +2072,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -2102,7 +2101,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -2131,7 +2130,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -2160,7 +2159,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -2189,7 +2188,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -2218,7 +2217,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -2247,7 +2246,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -2276,7 +2275,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -2305,7 +2304,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -2334,7 +2333,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -2363,7 +2362,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -2392,7 +2391,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -2421,7 +2420,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -2450,7 +2449,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -2479,7 +2478,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -2508,7 +2507,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -2537,7 +2536,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -2566,7 +2565,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -2595,7 +2594,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -2624,7 +2623,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -2653,7 +2652,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -2682,7 +2681,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -2711,7 +2710,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -2740,7 +2739,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -2769,7 +2768,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -2798,7 +2797,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -2827,7 +2826,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -2856,7 +2855,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="n">
+      <c r="A69" s="5" t="n">
         <v>46235</v>
       </c>
       <c r="B69" t="n">
@@ -2885,7 +2884,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="n">
+      <c r="A70" s="5" t="n">
         <v>46266</v>
       </c>
       <c r="B70" t="n">
@@ -2914,7 +2913,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="n">
+      <c r="A71" s="5" t="n">
         <v>46296</v>
       </c>
       <c r="B71" t="n">
